--- a/docs/ONC Hydrophones Specs.xlsx
+++ b/docs/ONC Hydrophones Specs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ebeaudin/Desktop/Hydrophones/hydrophone-handbook/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029699B6-38B1-F545-9ECA-F1F353BAC254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4ECB0E-6BDF-404D-9AA1-C7D487050582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37400" yWindow="1040" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -239,9 +239,6 @@
     <t>1 - 32 kS/s</t>
   </si>
   <si>
-    <t>Sensitivity (w/ pre-amp)</t>
-  </si>
-  <si>
     <t>-165 +/- 1</t>
   </si>
   <si>
@@ -266,25 +263,13 @@
     <t>Frequency Range</t>
   </si>
   <si>
-    <t>10 kHz - 200 kHz</t>
-  </si>
-  <si>
-    <t>10 Hz - 200 kHz (effective up to 128 kHz)</t>
-  </si>
-  <si>
     <t>Operating Temperatures</t>
   </si>
   <si>
-    <t>0°C to +35°C</t>
-  </si>
-  <si>
     <t>-40 to +70 °C</t>
   </si>
   <si>
     <t>-5 to +35°C</t>
-  </si>
-  <si>
-    <t>Max Humidity</t>
   </si>
   <si>
     <t>Storage Capacity</t>
@@ -300,10 +285,6 @@
 4.2 mA with current signalling pre-amp</t>
   </si>
   <si>
-    <t>1/3 mA at 6.8 VDC
-4.2 mA with currency signalling mode</t>
-  </si>
-  <si>
     <t>Input Voltage</t>
   </si>
   <si>
@@ -317,9 +298,6 @@
     <t>48V (36 V recommended)</t>
   </si>
   <si>
-    <t>Power (min, typical, max)</t>
-  </si>
-  <si>
     <t>(1.83, 2.26, 3.75)</t>
   </si>
   <si>
@@ -344,10 +322,32 @@
     <t>10 Hz - 12 kHz</t>
   </si>
   <si>
-    <t>0.1 - 1600 Hz (infrasound)</t>
-  </si>
-  <si>
     <t>1 Hz - 200 kHz</t>
+  </si>
+  <si>
+    <t>10 Hz - 200 kHz</t>
+  </si>
+  <si>
+    <t>0.1 - 1600 Hz</t>
+  </si>
+  <si>
+    <t>Audio-frequency, omnidirectional, piezoelectric</t>
+  </si>
+  <si>
+    <t>1.3 mA at 6.8 VDC
+4.2 mA with currency signalling mode</t>
+  </si>
+  <si>
+    <t>Max Humidity [%]</t>
+  </si>
+  <si>
+    <t>Sensitivity (w/ pre-amp) [dB re 1 V/µPa]</t>
+  </si>
+  <si>
+    <t>Power (min, typical, max) [W]</t>
+  </si>
+  <si>
+    <t>1 Hz - 170kHz</t>
   </si>
 </sst>
 </file>
@@ -466,7 +466,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,6 +477,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -492,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -552,6 +558,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -876,7 +888,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -1007,21 +1019,21 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7">
         <v>-173</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="23">
         <v>-169</v>
       </c>
       <c r="G9" s="8"/>
@@ -1033,22 +1045,22 @@
     </row>
     <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -1059,22 +1071,22 @@
     </row>
     <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -1085,22 +1097,22 @@
     </row>
     <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -1111,7 +1123,7 @@
     </row>
     <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="13"/>
@@ -1133,7 +1145,7 @@
     </row>
     <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>45</v>
@@ -1142,13 +1154,13 @@
         <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -1159,13 +1171,13 @@
     </row>
     <row r="15" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>45</v>
@@ -1185,22 +1197,22 @@
     </row>
     <row r="16" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -1211,18 +1223,18 @@
     </row>
     <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -1233,22 +1245,22 @@
     </row>
     <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -1259,22 +1271,22 @@
     </row>
     <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
